--- a/outputs/parsing_results.xlsx
+++ b/outputs/parsing_results.xlsx
@@ -1187,64 +1187,64 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, консультативно-диагностический центр</t>
+          <t>Клиническая больница им. Н.А. Семашко, физиотерапевтическая поликлиника</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 27, корп. 1, Ярославль</t>
+          <t>ул. Носкова, 8А, Ярославль</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 51-34-80, </t>
+          <t xml:space="preserve">+7 (4852) 75-58-15, </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_konsultativno_diagnosticheskiy_tsentr/1052993091/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_im_n_a_semashko_fizioterapevticheskaya_poliklinika/1732867406/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>http://odkb.yarneo3.tmweb.ru/</t>
+          <t>http://semashkoyar.ru/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская больница, Отделение больницы, госпиталя, Диагностический центр, </t>
+          <t xml:space="preserve">Поликлиника для взрослых, Больница для взрослых, Детская поликлиника, </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, поликлиника № 3</t>
+          <t>Областная детская клиническая больница, консультативно-диагностический центр</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 31, корп. 2, Ярославль, этаж 2</t>
+          <t>Тутаевское ш., 27, корп. 1, Ярославль</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 55-21-85, </t>
+          <t xml:space="preserve">+7 (4852) 51-34-80, </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_poliklinika_3/1037376162/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_konsultativno_diagnosticheskiy_tsentr/1052993091/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://кб9.рф/</t>
+          <t>http://odkb.yarneo3.tmweb.ru/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поликлиника для взрослых, Больница для взрослых, </t>
+          <t xml:space="preserve">Детская больница, Отделение больницы, госпиталя, Диагностический центр, </t>
         </is>
       </c>
     </row>
@@ -1283,32 +1283,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Клиническая больница им. Н.А. Семашко, физиотерапевтическая поликлиника</t>
+          <t>Клиническая больница № 9, поликлиника № 3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ул. Носкова, 8А, Ярославль</t>
+          <t>Тутаевское ш., 31, корп. 2, Ярославль, этаж 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 75-58-15, </t>
+          <t xml:space="preserve">+7 (4852) 55-21-85, </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_im_n_a_semashko_fizioterapevticheskaya_poliklinika/1732867406/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_poliklinika_3/1037376162/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>http://semashkoyar.ru/</t>
+          <t>https://кб9.рф/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поликлиника для взрослых, Больница для взрослых, Детская поликлиника, </t>
+          <t xml:space="preserve">Поликлиника для взрослых, Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -1635,64 +1635,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Клиническая больница № 2, родильный дом</t>
+          <t>Клиническая больница № 9, офис врача общей практики</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ул. Попова, 26, Ярославль</t>
+          <t>1-я ул. Кольцова, 40, Ярославль</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 46-28-68, </t>
+          <t xml:space="preserve">+7 (4852) 67-92-08, </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_rodilny_dom/1032084319/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_ofis_vracha_obshchey_praktiki/239215701367/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>http://www.kb2yar.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Родильный дом, Больница для взрослых, </t>
+          <t xml:space="preserve">Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, офис врача общей практики</t>
+          <t>Клиническая больница № 2, родильный дом</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1-я ул. Кольцова, 40, Ярославль</t>
+          <t>ул. Попова, 26, Ярославль</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 67-92-08, </t>
+          <t xml:space="preserve">+7 (4852) 46-28-68, </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_ofis_vracha_obshchey_praktiki/239215701367/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_rodilny_dom/1032084319/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://www.kb2yar.ru/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, </t>
+          <t xml:space="preserve">Родильный дом, Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -2499,96 +2499,96 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Клиническая больница имени Н.В. Соловьева, травматологическое отделение № 1</t>
+          <t>Клиническая больница № 9, стоматологическое отделение</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ул. Загородный Сад, 11, корп. 1, Ярославль, этаж 2</t>
+          <t>Тутаевское ш., 31, корп. 2, Ярославль, этаж 3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 73-38-19, </t>
+          <t xml:space="preserve">+7 (4852) 55-22-53, </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_v_solovyeva_travmatologicheskoye_otdeleniye_1/136739706466/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_stomatologicheskoye_otdeleniye/233055164112/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>http://bolnica-solovyeva-76.ru/chairs/1trauma</t>
+          <t>https://кб9.рф/</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Больница для взрослых, Поликлиника для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, стоматологическое отделение</t>
+          <t>Ярославская областная психиатрическая больница, диспансерное отделение для детей</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 31, корп. 2, Ярославль, этаж 3</t>
+          <t>ул. Зои Космодемьянской, 9, Ярославль</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 55-22-53, </t>
+          <t xml:space="preserve">+7 (4852) 73-85-23, </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_stomatologicheskoye_otdeleniye/233055164112/</t>
+          <t>https://yandex.ru/maps/org/yaroslavskaya_oblastnaya_psikhiatricheskaya_bolnitsa_dispansernoye_otdeleniye_dlya_detey/1147461422/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://кб9.рф/</t>
+          <t>http://www.yaokpb.ru/</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, Поликлиника для взрослых, </t>
+          <t xml:space="preserve">Детская больница, Специализированная больница, Диспансер, </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ярославская областная психиатрическая больница, диспансерное отделение для детей</t>
+          <t>Клиническая больница имени Н.В. Соловьева, травматологическое отделение № 1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ул. Зои Космодемьянской, 9, Ярославль</t>
+          <t>ул. Загородный Сад, 11, корп. 1, Ярославль, этаж 2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 73-85-23, </t>
+          <t xml:space="preserve">+7 (4852) 73-38-19, </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/yaroslavskaya_oblastnaya_psikhiatricheskaya_bolnitsa_dispansernoye_otdeleniye_dlya_detey/1147461422/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_v_solovyeva_travmatologicheskoye_otdeleniye_1/136739706466/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>http://www.yaokpb.ru/</t>
+          <t>http://bolnica-solovyeva-76.ru/chairs/1trauma</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская больница, Специализированная больница, Диспансер, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -2627,64 +2627,64 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Клиническая больница № 3, отделение врачей общей практики № 3</t>
+          <t>Клиническая больница № 2, приемное отделение</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Алмазная ул., 1, корп. 7, Ярославль</t>
+          <t>ул. Попова, 24, Ярославль, этаж 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 23-11-01, </t>
+          <t xml:space="preserve">+7 (4852) 46-29-59, </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_3_otdeleniye_vrachey_obshchey_praktiki_3/164363620233/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_priyemnoye_otdeleniye/198504378781/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://www.kb2yar.ru/</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, Поликлиника для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Клиническая больница № 2, приемное отделение</t>
+          <t>Клиническая больница № 3, отделение врачей общей практики № 3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ул. Попова, 24, Ярославль, этаж 1</t>
+          <t>Алмазная ул., 1, корп. 7, Ярославль</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 46-29-59, </t>
+          <t xml:space="preserve">+7 (4852) 23-11-01, </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_priyemnoye_otdeleniye/198504378781/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_3_otdeleniye_vrachey_obshchey_praktiki_3/164363620233/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>http://www.kb2yar.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, Поликлиника для взрослых, </t>
         </is>
       </c>
     </row>
@@ -3491,27 +3491,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>КБ им. Н. А. Семашко, отделение анестезиологии и реанимации</t>
+          <t>Клиническая больница имени Н.В. Соловьёва, травматологическое отделение № 12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ул. Семашко, 7, Ярославль, этаж 2</t>
+          <t>ул. Загородный Сад, 11, корп. 5, Ярославль</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 75-58-78, </t>
+          <t xml:space="preserve">+7 (4852) 73-28-86, </t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/kb_im_n_a_semashko_otdeleniye_anesteziologii_i_reanimatsii/106055924387/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_v_solovyova_travmatologicheskoye_otdeleniye_12/109735390956/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>http://semashkoyar.ru/</t>
+          <t>http://bolnica-solovyeva-76.ru/chairs/12trauma</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3523,27 +3523,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Клиническая больница имени Н.В. Соловьёва, травматологическое отделение № 12</t>
+          <t>КБ им. Н. А. Семашко, отделение анестезиологии и реанимации</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ул. Загородный Сад, 11, корп. 5, Ярославль</t>
+          <t>ул. Семашко, 7, Ярославль, этаж 2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 73-28-86, </t>
+          <t xml:space="preserve">+7 (4852) 75-58-78, </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_v_solovyova_travmatologicheskoye_otdeleniye_12/109735390956/</t>
+          <t>https://yandex.ru/maps/org/kb_im_n_a_semashko_otdeleniye_anesteziologii_i_reanimatsii/106055924387/</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>http://bolnica-solovyeva-76.ru/chairs/12trauma</t>
+          <t>http://semashkoyar.ru/</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4259,32 +4259,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ярославская областная клиническая туберкулезная больница, детское поликлиническое отделение</t>
+          <t>Областная клиническая больница, отделение сосудистой хирургии</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ул. Бабича, 3, Ярославль</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (930) 126-03-14, </t>
+          <t xml:space="preserve">+7 (4852) 58-91-56, </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/yaroslavskaya_oblastnaya_klinicheskaya_tuberkuleznaya_bolnitsa_detskoye_poliklinicheskoye_otdeleniye/1074115082/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_otdeleniye_sosudistoy_khirurgii/231433761542/</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://яоктб76.рф/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская поликлиника, Специализированная больница, Детская больница, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -4323,32 +4323,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, отделение сосудистой хирургии</t>
+          <t>Ярославская областная клиническая туберкулезная больница, детское поликлиническое отделение</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>ул. Бабича, 3, Ярославль</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-91-56, </t>
+          <t xml:space="preserve">+7 (930) 126-03-14, </t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_otdeleniye_sosudistoy_khirurgii/231433761542/</t>
+          <t>https://yandex.ru/maps/org/yaroslavskaya_oblastnaya_klinicheskaya_tuberkuleznaya_bolnitsa_detskoye_poliklinicheskoye_otdeleniye/1074115082/</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>https://яоктб76.рф/</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Детская поликлиника, Специализированная больница, Детская больница, </t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Клиническая больница № 2, отделение восстановительного лечения</t>
+          <t>Ярославский областной клинический госпиталь ветеранов войн, центр профилактики остеопороза</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Суздальское ш., 39, Ярославль</t>
+          <t>Угличская ул., 40, Ярославль</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4626,39 +4626,39 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_otdeleniye_vosstanovitelnogo_lecheniya/202565932513/</t>
+          <t>https://yandex.ru/maps/org/yaroslavskiy_oblastnoy_klinicheskiy_gospital_veteranov_voyn_tsentr_profilaktiki_osteoporoza/239295900887/</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>http://kb2yar.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, </t>
+          <t xml:space="preserve">Больница для взрослых, Специализированная больница, </t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ярославский областной клинический госпиталь ветеранов войн, центр профилактики остеопороза</t>
+          <t>КБ № 2, Кабинет МРТ</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Угличская ул., 40, Ярославль</t>
+          <t>Суздальское ш., 39, Ярославль</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Телефон отсутствует</t>
+          <t xml:space="preserve">+7 (4852) 44-68-22, </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/yaroslavskiy_oblastnoy_klinicheskiy_gospital_veteranov_voyn_tsentr_profilaktiki_osteoporoza/239295900887/</t>
+          <t>https://yandex.ru/maps/org/kb_2_kabinet_mrt/92826035831/</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, Специализированная больница, </t>
+          <t xml:space="preserve">Больница для взрослых, Магнитно-резонансная томография, </t>
         </is>
       </c>
     </row>
@@ -4739,64 +4739,64 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Клиническая больница им. Н. А. Семашко, женская консультация № 2</t>
+          <t>Центральная городская больница, детская поликлиника № 3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ул. Носкова, 8, Ярославль, этаж 1</t>
+          <t>ул. Чайковского, 78/19, Ярославль</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 75-58-07, </t>
+          <t xml:space="preserve">+7 (4852) 72-88-78, </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_im_n_a_semashko_zhenskaya_konsultatsiya_2/1049064489/</t>
+          <t>https://yandex.ru/maps/org/tsentralnaya_gorodskaya_bolnitsa_detskaya_poliklinika_3/1066571998/</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>http://semashkoyar.ru/</t>
+          <t>http://гбкузяоцгб.рф/</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Женская консультация, </t>
+          <t xml:space="preserve">Детская поликлиника, </t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Центральная городская больница, детская поликлиника № 3</t>
+          <t>Клиническая больница им. Н. А. Семашко, женская консультация № 2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ул. Чайковского, 78/19, Ярославль</t>
+          <t>ул. Носкова, 8, Ярославль, этаж 1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 72-88-78, </t>
+          <t xml:space="preserve">+7 (4852) 75-58-07, </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/tsentralnaya_gorodskaya_bolnitsa_detskaya_poliklinika_3/1066571998/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_im_n_a_semashko_zhenskaya_konsultatsiya_2/1049064489/</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>http://гбкузяоцгб.рф/</t>
+          <t>http://semashkoyar.ru/</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская поликлиника, </t>
+          <t xml:space="preserve">Женская консультация, </t>
         </is>
       </c>
     </row>
@@ -5027,64 +5027,64 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, хирургическое отделение</t>
+          <t>Клиническая больница имени Н.А. Семашко, стоматологическая поликлиника № 1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Аддрес отсутсвует</t>
+          <t>Институтская ул., 9, Ярославль</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 57-55-04, </t>
+          <t xml:space="preserve">+7 (4852) 44-26-76, </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_khirurgicheskoye_otdeleniye/204373368215/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_a_semashko_stomatologicheskaya_poliklinika_1/195601602740/</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://semashkoyar.ru/</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская больница, Отделение больницы, госпиталя, </t>
+          <t xml:space="preserve">Стоматологическая поликлиника, </t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Клиническая больница имени Н.А. Семашко, стоматологическая поликлиника № 1</t>
+          <t>Областная детская клиническая больница, хирургическое отделение</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Институтская ул., 9, Ярославль</t>
+          <t>Аддрес отсутсвует</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 44-26-76, </t>
+          <t xml:space="preserve">+7 (4852) 57-55-04, </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_a_semashko_stomatologicheskaya_poliklinika_1/195601602740/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_khirurgicheskoye_otdeleniye/204373368215/</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>http://semashkoyar.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стоматологическая поликлиника, </t>
+          <t xml:space="preserve">Детская больница, Отделение больницы, госпиталя, </t>
         </is>
       </c>
     </row>
@@ -5347,108 +5347,108 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Детская поликлиника № 1</t>
+          <t>Клиническая больница № 2, отделение восстановительного лечения</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ул. Чехова, 43, Ярославль</t>
+          <t>Суздальское ш., 39, Ярославль</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 20-83-27, </t>
+          <t>Телефон отсутствует</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/detskaya_poliklinika_1/70909381636/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_otdeleniye_vosstanovitelnogo_lecheniya/202565932513/</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>http://гбкузяоцгб.рф/</t>
+          <t>http://kb2yar.ru/</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская поликлиника, </t>
+          <t xml:space="preserve">Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>КБ № 2, Кабинет МРТ</t>
+          <t>Детская поликлиника № 1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Суздальское ш., 39, Ярославль</t>
+          <t>ул. Чехова, 43, Ярославль</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 44-68-22, </t>
+          <t xml:space="preserve">+7 (4852) 20-83-27, </t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/kb_2_kabinet_mrt/92826035831/</t>
+          <t>https://yandex.ru/maps/org/detskaya_poliklinika_1/70909381636/</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://гбкузяоцгб.рф/</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, Магнитно-резонансная томография, </t>
+          <t xml:space="preserve">Детская поликлиника, </t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ярославская центральная районная больница</t>
+          <t>Клиническая больница № 9, центр платных услуг</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>рабочий посёлок Лесная Поляна, 15</t>
+          <t>Тутаевское ш., 95, Ярославль, этаж 3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Телефон отсутствует</t>
+          <t xml:space="preserve">+7 (4852) 67-92-08, </t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/yaroslavskaya_tsentralnaya_rayonnaya_bolnitsa/193247348894/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_tsentr_platnykh_uslug/109531387215/</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://кб9.рф/</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Клиническая больница № 3, отделение анестезиологии и реанимации</t>
+          <t>Ярославская центральная районная больница</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ул. Здоровья, 10, корп. 1, Ярославль</t>
+          <t>рабочий посёлок Лесная Поляна, 15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_3_otdeleniye_anesteziologii_i_reanimatsii/28618009417/</t>
+          <t>https://yandex.ru/maps/org/yaroslavskaya_tsentralnaya_rayonnaya_bolnitsa/193247348894/</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5475,32 +5475,32 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, центр платных услуг</t>
+          <t>Клиническая больница № 3, отделение анестезиологии и реанимации</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 95, Ярославль, этаж 3</t>
+          <t>ул. Здоровья, 10, корп. 1, Ярославль</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 67-92-08, </t>
+          <t>Телефон отсутствует</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_tsentr_platnykh_uslug/109531387215/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_3_otdeleniye_anesteziologii_i_reanimatsii/28618009417/</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>http://кб9.рф/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -5987,27 +5987,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Больница имени Н.В. Соловьева, патологоанатомическое отделение</t>
+          <t>Клиническая больница № 2, пульмонологическое отделение</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ул. Загородный Сад, 11, корп. 8, Ярославль</t>
+          <t>ул. Попова, 24, Ярославль, этаж 4</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 71-52-03, </t>
+          <t xml:space="preserve">+7 (4852) 28-40-30, </t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/bolnitsa_imeni_n_v_solovyeva_patologoanatomicheskoye_otdeleniye/94848319062/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_pulmonologicheskoye_otdeleniye/106828412936/</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>http://bolnica-solovyeva-76.ru/chairs/pathologist</t>
+          <t>http://www.kb2yar.ru/</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6019,27 +6019,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Клиническая больница № 2, пульмонологическое отделение</t>
+          <t>Больница имени Н.В. Соловьева, патологоанатомическое отделение</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ул. Попова, 24, Ярославль, этаж 4</t>
+          <t>ул. Загородный Сад, 11, корп. 8, Ярославль</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 28-40-30, </t>
+          <t xml:space="preserve">+7 (4852) 71-52-03, </t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_2_pulmonologicheskoye_otdeleniye/106828412936/</t>
+          <t>https://yandex.ru/maps/org/bolnitsa_imeni_n_v_solovyeva_patologoanatomicheskoye_otdeleniye/94848319062/</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>http://www.kb2yar.ru/</t>
+          <t>http://bolnica-solovyeva-76.ru/chairs/pathologist</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6787,27 +6787,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Патологоанатомическое отделение</t>
+          <t>Рентгенологическое отделение</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 31В, Ярославль</t>
+          <t>ул. Загородный Сад, 11, корп. 5, Ярославль</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 78-81-69, </t>
+          <t xml:space="preserve">+7 (4852) 25-14-43, </t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/patologoanatomicheskoye_otdeleniye/37391235211/</t>
+          <t>https://yandex.ru/maps/org/rentgenologicheskoye_otdeleniye/231593855805/</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://opcyar.ru/</t>
+          <t>http://bolnica-solovyeva-76.ru/chairs/x_ray/</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -6819,32 +6819,32 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Рентгенологическое отделение</t>
+          <t>Областная клиническая онкологическая больница, торакальное отделение</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ул. Загородный Сад, 11, корп. 5, Ярославль</t>
+          <t>просп. Октября, 67, корп. 3, Ярославль</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 25-14-43, </t>
+          <t xml:space="preserve">+7 (4852) 20-81-00, </t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/rentgenologicheskoye_otdeleniye/231593855805/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_onkologicheskaya_bolnitsa_torakalnoye_otdeleniye/235450592601/</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>http://bolnica-solovyeva-76.ru/chairs/x_ray/</t>
+          <t>http://onkoyar.ru/</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, </t>
         </is>
       </c>
     </row>
@@ -6979,64 +6979,64 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Областная клиническая онкологическая больница, торакальное отделение</t>
+          <t>Областная детская клиническая больница, отделение патологии новорожденных</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>просп. Октября, 67, корп. 3, Ярославль</t>
+          <t>Тутаевское ш., 27, корп. 2, Ярославль</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 20-81-00, </t>
+          <t xml:space="preserve">+7 (4852) 55-08-80, </t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_onkologicheskaya_bolnitsa_torakalnoye_otdeleniye/235450592601/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otdeleniye_patologii_novorozhdennykh/126966536694/</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>http://onkoyar.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, отделение патологии новорожденных</t>
+          <t>Патологоанатомическое отделение</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 27, корп. 2, Ярославль</t>
+          <t>Тутаевское ш., 31В, Ярославль</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 55-08-80, </t>
+          <t xml:space="preserve">+7 (4852) 78-81-69, </t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otdeleniye_patologii_novorozhdennykh/126966536694/</t>
+          <t>https://yandex.ru/maps/org/patologoanatomicheskoye_otdeleniye/37391235211/</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>https://opcyar.ru/</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -7683,22 +7683,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, гематологическое отделение</t>
+          <t>Эндокринологическое отделение</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>Яковлевская ул., 7, корп. 6, Ярославль, кабинет 312-314, этаж 3</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-91-65, </t>
+          <t xml:space="preserve">+7 (4852) 58-23-40, </t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_gematologicheskoye_otdeleniye/228987316524/</t>
+          <t>https://yandex.ru/maps/org/endokrinologicheskoye_otdeleniye/231399365116/</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7715,22 +7715,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Эндокринологическое отделение</t>
+          <t>Областная клиническая больница, гематологическое отделение</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, корп. 6, Ярославль, кабинет 312-314, этаж 3</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-23-40, </t>
+          <t xml:space="preserve">+7 (4852) 58-91-65, </t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/endokrinologicheskoye_otdeleniye/231399365116/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_gematologicheskoye_otdeleniye/228987316524/</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8035,155 +8035,155 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Центр платных услуг</t>
+          <t>Клиническая больница № 9, физиотерапевтическое отделение</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>Тутаевское ш., 95, Ярославль, этаж 2</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-23-20, </t>
+          <t xml:space="preserve">+7 (4852) 67-92-08, </t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/tsentr_platnykh_uslug/13080197599/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_fizioterapevticheskoye_otdeleniye/27015880034/</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>https://yaokb.zdrav76.ru/</t>
+          <t>http://кб9.рф/</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Диагностический центр, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, физиотерапевтическое отделение</t>
+          <t>Центр платных услуг</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 95, Ярославль, этаж 2</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 67-92-08, </t>
+          <t xml:space="preserve">+7 (4852) 58-23-20, </t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_fizioterapevticheskoye_otdeleniye/27015880034/</t>
+          <t>https://yandex.ru/maps/org/tsentr_platnykh_uslug/13080197599/</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>http://кб9.рф/</t>
+          <t>https://yaokb.zdrav76.ru/</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Диагностический центр, </t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, стоматологическая поликлиника № 4</t>
+          <t>Ярославская областная клиническая туберкулёзная больница, детское легочно-туберкулезное отделение</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>3-й Норский пер., 9, посёлок Норское, Ярославль</t>
+          <t>Аддрес отсутсвует</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 97-35-59, </t>
+          <t>Телефон отсутствует</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_stomatologicheskaya_poliklinika_4/1043593590/</t>
+          <t>https://yandex.ru/maps/org/yaroslavskaya_oblastnaya_klinicheskaya_tuberkulyoznaya_bolnitsa_detskoye_legochno_tuberkuleznoye_otdeleniye/132018167180/</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>http://кб9.рф/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Стоматологическая поликлиника, </t>
+          <t xml:space="preserve">Специализированная больница, Отделение больницы, госпиталя, </t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Ярославская областная клиническая туберкулёзная больница, детское легочно-туберкулезное отделение</t>
+          <t>Областной перинатальный центр, отделение анестезиологии-реанимации</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Аддрес отсутсвует</t>
+          <t>Тутаевское ш., 31В, Ярославль</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Телефон отсутствует</t>
+          <t xml:space="preserve">+7 (4852) 78-81-40, </t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/yaroslavskaya_oblastnaya_klinicheskaya_tuberkulyoznaya_bolnitsa_detskoye_legochno_tuberkuleznoye_otdeleniye/132018167180/</t>
+          <t>https://yandex.ru/maps/org/oblastnoy_perinatalny_tsentr_otdeleniye_anesteziologii_reanimatsii/119337281551/</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://opcyar.ru/</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Специализированная больница, Отделение больницы, госпиталя, </t>
+          <t xml:space="preserve">Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Областной перинатальный центр, отделение анестезиологии-реанимации</t>
+          <t>Клиническая больница скорой медицинской помощи им. Н. В. Соловьева, терапевтическое отделение № 12</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 31В, Ярославль</t>
+          <t>ул. Загородный Сад, 11, корп. 11, Ярославль</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 78-81-40, </t>
+          <t>Телефон отсутствует</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnoy_perinatalny_tsentr_otdeleniye_anesteziologii_reanimatsii/119337281551/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_skoroy_meditsinskoy_pomoshchi_im_n_v_solovyeva_terapevticheskoye_otdeleniye_12/163771700432/</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>http://opcyar.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8195,22 +8195,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Клиническая больница скорой медицинской помощи им. Н. В. Соловьева, терапевтическое отделение № 12</t>
+          <t>Областная клиническая больница, колопроктологическое отделение</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ул. Загородный Сад, 11, корп. 11, Ярославль</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Телефон отсутствует</t>
+          <t xml:space="preserve">+7 (4852) 58-91-46, </t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_skoroy_meditsinskoy_pomoshchi_im_n_v_solovyeva_terapevticheskoye_otdeleniye_12/163771700432/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_koloproktologicheskoye_otdeleniye/114949317927/</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8220,71 +8220,71 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, колопроктологическое отделение</t>
+          <t>Инфекционная клиническая больница № 1, реанимационное отделение</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>просп. Октября, 54/5, Ярославль</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-91-46, </t>
+          <t xml:space="preserve">+7 (4852) 73-94-69, </t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_koloproktologicheskoye_otdeleniye/114949317927/</t>
+          <t>https://yandex.ru/maps/org/infektsionnaya_klinicheskaya_bolnitsa_1_reanimatsionnoye_otdeleniye/28180268619/</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://ikb76.ru/</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Специализированная больница, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Инфекционная клиническая больница № 1, реанимационное отделение</t>
+          <t>Клиническая больница № 9, стоматологическая поликлиника № 4</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>просп. Октября, 54/5, Ярославль</t>
+          <t>3-й Норский пер., 9, посёлок Норское, Ярославль</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 73-94-69, </t>
+          <t xml:space="preserve">+7 (4852) 97-35-59, </t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/infektsionnaya_klinicheskaya_bolnitsa_1_reanimatsionnoye_otdeleniye/28180268619/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_stomatologicheskaya_poliklinika_4/1043593590/</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>http://ikb76.ru/</t>
+          <t>http://кб9.рф/</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Специализированная больница, Больница для взрослых, </t>
+          <t xml:space="preserve">Стоматологическая поликлиника, </t>
         </is>
       </c>
     </row>
@@ -8547,96 +8547,96 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Центральная городская больница, детская поликлиника № 1</t>
+          <t>Клиническая больница скорой медицинской помощи им. Н. В. Соловьева, Травматологическое отделение № 1</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>ул. Терешковой, 22, Ярославль</t>
+          <t>Аддрес отсутсвует</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 25-23-54, </t>
+          <t>Телефон отсутствует</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/tsentralnaya_gorodskaya_bolnitsa_detskaya_poliklinika_1/175436547632/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_skoroy_meditsinskoy_pomoshchi_im_n_v_solovyeva_travmatologicheskoye_otdeleniye_1/18492804612/</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>https://гбкузяоцгб.рф/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская поликлиника, </t>
+          <t xml:space="preserve">Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Клиническая больница № 9, отделение для пациентов с признаками ОРВИ</t>
+          <t>Центральная городская больница, детская поликлиника № 1</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 95, Ярославль</t>
+          <t>ул. Терешковой, 22, Ярославль</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 54-11-14, </t>
+          <t xml:space="preserve">+7 (4852) 25-23-54, </t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_otdeleniye_dlya_patsiyentov_s_priznakami_orvi/227204017334/</t>
+          <t>https://yandex.ru/maps/org/tsentralnaya_gorodskaya_bolnitsa_detskaya_poliklinika_1/175436547632/</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>https://кб9.рф/</t>
+          <t>https://гбкузяоцгб.рф/</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, </t>
+          <t xml:space="preserve">Детская поликлиника, </t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Клиническая больница скорой медицинской помощи им. Н. В. Соловьева, Травматологическое отделение № 1</t>
+          <t>Клиническая больница № 9, отделение для пациентов с признаками ОРВИ</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Аддрес отсутсвует</t>
+          <t>Тутаевское ш., 95, Ярославль</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Телефон отсутствует</t>
+          <t xml:space="preserve">+7 (4852) 54-11-14, </t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_skoroy_meditsinskoy_pomoshchi_im_n_v_solovyeva_travmatologicheskoye_otdeleniye_1/18492804612/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_9_otdeleniye_dlya_patsiyentov_s_priznakami_orvi/227204017334/</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>https://кб9.рф/</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, </t>
         </is>
       </c>
     </row>
@@ -8675,22 +8675,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, кардиохирургическое отделение</t>
+          <t>ГУЗ больница № 7 отделение анестезии и реанимации</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>ул. Здоровья, 10, корп. 1, Ярославль</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-90-91, </t>
+          <t>Телефон отсутствует</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_kardiokhirurgicheskoye_otdeleniye/42009817614/</t>
+          <t>https://yandex.ru/maps/org/guz_bolnitsa_7_otdeleniye_anestezii_i_reanimatsii/73447430444/</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8739,22 +8739,22 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ГУЗ больница № 7 отделение анестезии и реанимации</t>
+          <t>Областная клиническая больница, кардиохирургическое отделение</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ул. Здоровья, 10, корп. 1, Ярославль</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Телефон отсутствует</t>
+          <t xml:space="preserve">+7 (4852) 58-90-91, </t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/guz_bolnitsa_7_otdeleniye_anestezii_i_reanimatsii/73447430444/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_kardiokhirurgicheskoye_otdeleniye/42009817614/</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -8995,64 +8995,64 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Клиническая больница имени Н.В. Соловьева, физиотерапевтическое отделение</t>
+          <t>Женская консультация</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>ул. Загородный Сад, 11, корп. 1, Ярославль, этаж 1</t>
+          <t>ул. Гагарина, 12, корп. 1, Ярославль</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 73-26-75, </t>
+          <t xml:space="preserve">+7 (4852) 44-24-23, </t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_v_solovyeva_fizioterapevticheskoye_otdeleniye/142734253538/</t>
+          <t>https://yandex.ru/maps/org/zhenskaya_konsultatsiya/153292803342/</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>http://bolnica-solovyeva-76.ru/chairs/physiotherapy</t>
+          <t>http://semashkoyar.ru/</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Женская консультация, </t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Женская консультация</t>
+          <t>Клиническая больница имени Н.В. Соловьева, физиотерапевтическое отделение</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>ул. Гагарина, 12, корп. 1, Ярославль</t>
+          <t>ул. Загородный Сад, 11, корп. 1, Ярославль, этаж 1</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 44-24-23, </t>
+          <t xml:space="preserve">+7 (4852) 73-26-75, </t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/zhenskaya_konsultatsiya/153292803342/</t>
+          <t>https://yandex.ru/maps/org/klinicheskaya_bolnitsa_imeni_n_v_solovyeva_fizioterapevticheskoye_otdeleniye/142734253538/</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>http://semashkoyar.ru/</t>
+          <t>http://bolnica-solovyeva-76.ru/chairs/physiotherapy</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Женская консультация, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
@@ -10115,135 +10115,135 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, отделение лабораторной диагностики</t>
+          <t>Областная детская клиническая больница, уроандрологическое отделение</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 27, Ярославль, комната 109,111,219, этаж 1</t>
+          <t>Аддрес отсутсвует</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 51-34-79, </t>
+          <t xml:space="preserve">+7 (4852) 57-55-04, </t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otdeleniye_laboratornoy_diagnostiki/177246161684/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_uroandrologicheskoye_otdeleniye/159272731053/</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>https://odkb76.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Диагностический центр, </t>
+          <t xml:space="preserve">Детская больница, Отделение больницы, госпиталя, Курьерские услуги, </t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, отделение патологии речи и других высших психических функций</t>
+          <t>Областная клиническая больница, рентгенологическое отделение</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 29, Ярославль</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 55-09-34, </t>
+          <t xml:space="preserve">+7 (4852) 58-02-39, </t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otdeleniye_patologii_rechi_i_drugikh_vysshikh_psikhicheskikh_funktsiy/88435026619/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_rentgenologicheskoye_otdeleniye/8769610977/</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>https://odkb76.ru/</t>
+          <t>http://яокб.рф/параклинические-отделения/рентгенологическое-отделение/</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, кардиологическое отделение № 2 с палатой реанимации и интенсивной терапии</t>
+          <t>Областная детская клиническая больница, отделение лабораторной диагностики</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>Тутаевское ш., 27, Ярославль, комната 109,111,219, этаж 1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-91-09, </t>
+          <t xml:space="preserve">+7 (4852) 51-34-79, </t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_kardiologicheskoye_otdeleniye_2_s_palatoy_reanimatsii_i_intensivnoy_terapii/102745426895/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otdeleniye_laboratornoy_diagnostiki/177246161684/</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>https://odkb76.ru/</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Диагностический центр, </t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, уроандрологическое отделение</t>
+          <t>Областная детская клиническая больница, отделение патологии речи и других высших психических функций</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Аддрес отсутсвует</t>
+          <t>Тутаевское ш., 29, Ярославль</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 57-55-04, </t>
+          <t xml:space="preserve">+7 (4852) 55-09-34, </t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_uroandrologicheskoye_otdeleniye/159272731053/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otdeleniye_patologii_rechi_i_drugikh_vysshikh_psikhicheskikh_funktsiy/88435026619/</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>https://odkb76.ru/</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская больница, Отделение больницы, госпиталя, Курьерские услуги, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, физиотерапевтическое отделение</t>
+          <t>Областная клиническая больница, кардиологическое отделение № 2 с палатой реанимации и интенсивной терапии</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-91-77, </t>
+          <t xml:space="preserve">+7 (4852) 58-91-09, </t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_fizioterapevticheskoye_otdeleniye/90256213719/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_kardiologicheskoye_otdeleniye_2_s_palatoy_reanimatsii_i_intensivnoy_terapii/102745426895/</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10275,7 +10275,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, нейрохирургическое отделение № 2</t>
+          <t>Областная клиническая больница, физиотерапевтическое отделение</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-97-79, </t>
+          <t xml:space="preserve">+7 (4852) 58-91-77, </t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_neyrokhirurgicheskoye_otdeleniye_2/106764583973/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_fizioterapevticheskoye_otdeleniye/90256213719/</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10307,7 +10307,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, кардиологическое отделение № 1</t>
+          <t>Областная клиническая больница, нейрохирургическое отделение № 2</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-23-42, </t>
+          <t xml:space="preserve">+7 (4852) 58-97-79, </t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_kardiologicheskoye_otdeleniye_1/131006937381/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_neyrokhirurgicheskoye_otdeleniye_2/106764583973/</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10339,118 +10339,118 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ОДКБ, нефрологическое отделение</t>
+          <t>Областная клиническая больница, кардиологическое отделение № 1</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 29, Ярославль, этаж 1</t>
+          <t>Яковлевская ул., 7, Ярославль</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 55-18-64, </t>
+          <t xml:space="preserve">+7 (4852) 58-23-42, </t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/odkb_nefrologicheskoye_otdeleniye/193166370067/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_kardiologicheskoye_otdeleniye_1/131006937381/</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>https://odkb76.ru/</t>
+          <t>Ссылка на сайт отсутсвует</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Детская поликлиника КБ № 10, Лечебное отделение</t>
+          <t>ОДКБ, нефрологическое отделение</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ул. Гагарина, 12, корп. 2, Ярославль</t>
+          <t>Тутаевское ш., 29, Ярославль, этаж 1</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 44-26-86, </t>
+          <t xml:space="preserve">+7 (4852) 55-18-64, </t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/detskaya_poliklinika_kb_10_lechebnoye_otdeleniye/218668688516/</t>
+          <t>https://yandex.ru/maps/org/odkb_nefrologicheskoye_otdeleniye/193166370067/</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>http://semashkoyar.ru/</t>
+          <t>https://odkb76.ru/</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Медцентр, клиника, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Областная детская клиническая больница, оториноларингологическое отделение</t>
+          <t>Детская поликлиника КБ № 10, Лечебное отделение</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Тутаевское ш., 27, корп. 1, Ярославль</t>
+          <t>ул. Гагарина, 12, корп. 2, Ярославль</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 57-55-04, </t>
+          <t xml:space="preserve">+7 (4852) 44-26-86, </t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otorinolaringologicheskoye_otdeleniye/38353779713/</t>
+          <t>https://yandex.ru/maps/org/detskaya_poliklinika_kb_10_lechebnoye_otdeleniye/218668688516/</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Ссылка на сайт отсутсвует</t>
+          <t>http://semashkoyar.ru/</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Медцентр, клиника, </t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Областная клиническая больница, рентгенологическое отделение</t>
+          <t>Областная детская клиническая больница, оториноларингологическое отделение</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Яковлевская ул., 7, Ярославль</t>
+          <t>Тутаевское ш., 27, корп. 1, Ярославль</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">+7 (4852) 58-02-39, </t>
+          <t xml:space="preserve">+7 (4852) 57-55-04, </t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://yandex.ru/maps/org/oblastnaya_klinicheskaya_bolnitsa_rentgenologicheskoye_otdeleniye/8769610977/</t>
+          <t>https://yandex.ru/maps/org/oblastnaya_detskaya_klinicheskaya_bolnitsa_otorinolaringologicheskoye_otdeleniye/38353779713/</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отделение больницы, госпиталя, Больница для взрослых, </t>
+          <t xml:space="preserve">Отделение больницы, госпиталя, Детская больница, </t>
         </is>
       </c>
     </row>
